--- a/extraction_script/data/تراز 98.xlsx
+++ b/extraction_script/data/تراز 98.xlsx
@@ -5,29 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreeN\Downloads\Eitaa Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting1\extraction_script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D9F6399-01C4-4225-A6A3-CEE16D4D3B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B94C91-D553-46DC-8991-E4EBD1DCC64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{CCEEFA5F-CD9F-48DD-934D-50F8D0C227A4}"/>
+    <workbookView xWindow="13965" yWindow="0" windowWidth="14835" windowHeight="16200" activeTab="1" xr2:uid="{CCEEFA5F-CD9F-48DD-934D-50F8D0C227A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="کل" sheetId="1" r:id="rId1"/>
-    <sheet name="معین" sheetId="2" r:id="rId2"/>
+    <sheet name="ک" sheetId="1" r:id="rId1"/>
+    <sheet name="م" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="101716"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
